--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1.xlsx
@@ -2344,7 +2344,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2524,6 +2524,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2533,7 +2536,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2713,6 +2716,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>120000</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>122000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2755,7 +2761,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2935,6 +2941,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2944,7 +2953,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3124,6 +3133,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>187206.43969950231</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>193867.80757147254</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3166,7 +3178,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3346,6 +3358,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3355,7 +3370,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3535,6 +3550,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>67206.439699502313</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>71867.807571472542</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3556,11 +3574,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="161226752"/>
-        <c:axId val="161228288"/>
+        <c:axId val="479043968"/>
+        <c:axId val="479045888"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="161226752"/>
+        <c:axId val="479043968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3603,14 +3621,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="161228288"/>
+        <c:crossAx val="479045888"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="161228288"/>
+        <c:axId val="479045888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3661,7 +3679,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="161226752"/>
+        <c:crossAx val="479043968"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3830,7 +3848,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4010,6 +4028,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4019,7 +4040,7 @@
               <c:f>'model1&amp;CCI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4198,6 +4219,9 @@
                   <c:v>26000</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>26000</c:v>
                 </c:pt>
               </c:numCache>
@@ -4241,7 +4265,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4421,6 +4445,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4430,7 +4457,7 @@
               <c:f>'model1&amp;CCI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4610,6 +4637,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>43140.497081088128</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>44214.678756661888</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4652,7 +4682,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4832,6 +4862,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4841,7 +4874,7 @@
               <c:f>'model1&amp;CCI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5021,6 +5054,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>17140.497081088128</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>18214.678756661888</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5042,11 +5078,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="426123264"/>
-        <c:axId val="426124800"/>
+        <c:axId val="517932160"/>
+        <c:axId val="517933696"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="426123264"/>
+        <c:axId val="517932160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5089,14 +5125,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426124800"/>
+        <c:crossAx val="517933696"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="426124800"/>
+        <c:axId val="517933696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5147,7 +5183,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426123264"/>
+        <c:crossAx val="517932160"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5316,7 +5352,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5496,6 +5532,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5505,7 +5544,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5685,6 +5724,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>129000</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>131000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5727,7 +5769,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5907,6 +5949,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5916,7 +5961,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6096,6 +6141,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>201026.69016266201</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>208032.17692068638</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6138,7 +6186,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6318,6 +6366,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6327,7 +6378,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6507,6 +6558,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>72026.690162662009</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>77032.176920686383</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6528,11 +6582,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="442375552"/>
-        <c:axId val="448738816"/>
+        <c:axId val="623968256"/>
+        <c:axId val="623970944"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="442375552"/>
+        <c:axId val="623968256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6575,14 +6629,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="448738816"/>
+        <c:crossAx val="623970944"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="448738816"/>
+        <c:axId val="623970944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6633,7 +6687,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="442375552"/>
+        <c:crossAx val="623968256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6802,7 +6856,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6982,6 +7036,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6991,7 +7048,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7171,6 +7228,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>122000</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>124000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7213,7 +7273,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7393,6 +7453,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7402,7 +7465,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7582,6 +7645,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>190997.66079790759</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>197753.4286074655</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7624,7 +7690,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7804,6 +7870,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7813,7 +7882,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7993,6 +8062,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>68997.660797907592</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>73753.428607465496</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8014,11 +8086,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="524067584"/>
-        <c:axId val="524069120"/>
+        <c:axId val="502106368"/>
+        <c:axId val="502112256"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="524067584"/>
+        <c:axId val="502106368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8061,14 +8133,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="524069120"/>
+        <c:crossAx val="502112256"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="524069120"/>
+        <c:axId val="502112256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8119,7 +8191,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="524067584"/>
+        <c:crossAx val="502106368"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8288,7 +8360,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8468,6 +8540,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8477,7 +8552,7 @@
               <c:f>'model1&amp;pe'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8657,6 +8732,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>120000</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>122000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8699,7 +8777,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8879,6 +8957,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8888,7 +8969,7 @@
               <c:f>'model1&amp;pe'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -9068,6 +9149,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>187206.43969950231</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>193867.80757147254</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9110,7 +9194,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9290,6 +9374,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9299,7 +9386,7 @@
               <c:f>'model1&amp;pe'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9479,6 +9566,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>67206.439699502313</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>71867.807571472542</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9500,11 +9590,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="472297472"/>
-        <c:axId val="472299008"/>
+        <c:axId val="502048640"/>
+        <c:axId val="502050176"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="472297472"/>
+        <c:axId val="502048640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9547,14 +9637,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472299008"/>
+        <c:crossAx val="502050176"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="472299008"/>
+        <c:axId val="502050176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9605,7 +9695,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="472297472"/>
+        <c:crossAx val="502048640"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10159,7 +10249,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12222,6 +12312,35 @@
         <v>67206.439699502313</v>
       </c>
     </row>
+    <row r="63" spans="1:9" ht="12.75">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="16">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D63" s="18">
+        <v>1567.3980910071355</v>
+      </c>
+      <c r="E63" s="18">
+        <v>151934.01574763237</v>
+      </c>
+      <c r="F63" s="18">
+        <v>193867.80757147254</v>
+      </c>
+      <c r="G63" s="18">
+        <v>122000</v>
+      </c>
+      <c r="H63" s="18">
+        <v>193867.80757147254</v>
+      </c>
+      <c r="I63" s="18">
+        <v>71867.807571472542</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12233,7 +12352,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14462,6 +14581,38 @@
         <v>107.7933992308817</v>
       </c>
     </row>
+    <row r="63" spans="1:10" ht="12.75">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="16">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="17">
+        <v>0</v>
+      </c>
+      <c r="D63" s="18">
+        <v>0</v>
+      </c>
+      <c r="E63" s="18">
+        <v>34651.001538842793</v>
+      </c>
+      <c r="F63" s="18">
+        <v>44214.678756661888</v>
+      </c>
+      <c r="G63" s="18">
+        <v>26000</v>
+      </c>
+      <c r="H63" s="18">
+        <v>44214.678756661888</v>
+      </c>
+      <c r="I63" s="18">
+        <v>18214.678756661888</v>
+      </c>
+      <c r="J63" s="6">
+        <v>66.335527216233743</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14473,7 +14624,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH62"/>
+  <dimension ref="A1:AH63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -17420,6 +17571,50 @@
         <v>86.230028778736084</v>
       </c>
     </row>
+    <row r="63" spans="1:14" ht="12.75">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="16">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D63" s="18">
+        <v>1567.3980910071355</v>
+      </c>
+      <c r="E63" s="18">
+        <v>163034.61848677124</v>
+      </c>
+      <c r="F63" s="18">
+        <v>208032.17692068638</v>
+      </c>
+      <c r="G63" s="18">
+        <v>131000</v>
+      </c>
+      <c r="H63" s="18">
+        <v>208032.17692068638</v>
+      </c>
+      <c r="I63" s="18">
+        <v>77032.176920686383</v>
+      </c>
+      <c r="J63" s="6">
+        <v>3.1000018119812012E-2</v>
+      </c>
+      <c r="K63" s="6">
+        <v>4.1362846399915991E-2</v>
+      </c>
+      <c r="L63" s="6">
+        <v>3.1000018119812012E-2</v>
+      </c>
+      <c r="M63" s="6">
+        <v>4.7142971012196826E-2</v>
+      </c>
+      <c r="N63" s="1">
+        <v>87.739159225273681</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17431,7 +17626,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH62"/>
+  <dimension ref="A1:AH63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20941,6 +21136,59 @@
         <v>94.913940221952458</v>
       </c>
     </row>
+    <row r="63" spans="1:17" ht="12.75">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="16">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D63" s="18">
+        <v>1567.3980910071355</v>
+      </c>
+      <c r="E63" s="18">
+        <v>154979.17324472862</v>
+      </c>
+      <c r="F63" s="18">
+        <v>197753.4286074655</v>
+      </c>
+      <c r="G63" s="18">
+        <v>124000</v>
+      </c>
+      <c r="H63" s="18">
+        <v>197753.4286074655</v>
+      </c>
+      <c r="I63" s="18">
+        <v>73753.428607465496</v>
+      </c>
+      <c r="J63" s="6">
+        <v>1.2970000505447388</v>
+      </c>
+      <c r="K63" s="6">
+        <v>1.1710000038146973</v>
+      </c>
+      <c r="L63" s="6">
+        <v>1.2970000505447388</v>
+      </c>
+      <c r="M63" s="6">
+        <v>1</v>
+      </c>
+      <c r="N63" s="6">
+        <v>92.929284820646245</v>
+      </c>
+      <c r="O63" s="6">
+        <v>89.001223655693991</v>
+      </c>
+      <c r="P63" s="6">
+        <v>85.066287551131708</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>96.871095864818557</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20952,7 +21200,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -23198,6 +23446,38 @@
         <v>67206.439699502313</v>
       </c>
     </row>
+    <row r="63" spans="1:10" ht="12.75">
+      <c r="A63" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="16">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="16">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E63" s="18">
+        <v>1567.3980910071355</v>
+      </c>
+      <c r="F63" s="18">
+        <v>151934.01574763237</v>
+      </c>
+      <c r="G63" s="18">
+        <v>193867.80757147254</v>
+      </c>
+      <c r="H63" s="18">
+        <v>122000</v>
+      </c>
+      <c r="I63" s="18">
+        <v>193867.80757147254</v>
+      </c>
+      <c r="J63" s="18">
+        <v>71867.807571472542</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J2"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1.xlsx
@@ -2344,7 +2344,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2527,6 +2527,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2536,7 +2539,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2719,6 +2722,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>122000</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>124000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2761,7 +2767,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2944,6 +2950,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2953,7 +2962,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3136,6 +3145,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>193867.80757147254</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>170190.95441836005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3178,7 +3190,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3361,6 +3373,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3370,7 +3385,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3553,6 +3568,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>71867.807571472542</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46190.954418360052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3574,11 +3592,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="479043968"/>
-        <c:axId val="479045888"/>
+        <c:axId val="548641024"/>
+        <c:axId val="566140928"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="479043968"/>
+        <c:axId val="548641024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3621,14 +3639,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479045888"/>
+        <c:crossAx val="566140928"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="479045888"/>
+        <c:axId val="566140928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3679,7 +3697,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479043968"/>
+        <c:crossAx val="548641024"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3848,7 +3866,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4031,6 +4049,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4040,7 +4061,7 @@
               <c:f>'model1&amp;CCI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4222,6 +4243,9 @@
                   <c:v>26000</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>26000</c:v>
                 </c:pt>
               </c:numCache>
@@ -4265,7 +4289,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4448,6 +4472,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4457,7 +4484,7 @@
               <c:f>'model1&amp;CCI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4640,6 +4667,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>44214.678756661888</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>38358.658472178577</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4682,7 +4712,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4865,6 +4895,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4874,7 +4907,7 @@
               <c:f>'model1&amp;CCI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5057,6 +5090,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>18214.678756661888</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>12358.658472178577</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5078,11 +5114,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="517932160"/>
-        <c:axId val="517933696"/>
+        <c:axId val="676456704"/>
+        <c:axId val="678416384"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="517932160"/>
+        <c:axId val="676456704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5125,14 +5161,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="517933696"/>
+        <c:crossAx val="678416384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="517933696"/>
+        <c:axId val="678416384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5183,7 +5219,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="517932160"/>
+        <c:crossAx val="676456704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5352,7 +5388,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5535,6 +5571,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5544,7 +5583,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5727,6 +5766,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>131000</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>133000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5769,7 +5811,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5952,6 +5994,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5961,7 +6006,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6144,6 +6189,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>208032.17692068638</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>182479.32157648227</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6186,7 +6234,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6369,6 +6417,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6378,7 +6429,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6561,6 +6612,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>77032.176920686383</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>49479.321576482267</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6582,11 +6636,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="623968256"/>
-        <c:axId val="623970944"/>
+        <c:axId val="80539648"/>
+        <c:axId val="80541184"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="623968256"/>
+        <c:axId val="80539648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6629,14 +6683,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="623970944"/>
+        <c:crossAx val="80541184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="623970944"/>
+        <c:axId val="80541184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6687,7 +6741,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="623968256"/>
+        <c:crossAx val="80539648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6856,7 +6910,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7039,6 +7093,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7048,7 +7105,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7231,6 +7288,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>124000</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>126000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7273,7 +7333,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7456,6 +7516,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7465,7 +7528,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7648,6 +7711,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>197753.4286074655</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>173561.94374731698</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7690,7 +7756,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7873,6 +7939,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7882,7 +7951,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8065,6 +8134,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>73753.428607465496</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>47561.943747316982</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8086,11 +8158,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="502106368"/>
-        <c:axId val="502112256"/>
+        <c:axId val="90145920"/>
+        <c:axId val="90147456"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="502106368"/>
+        <c:axId val="90145920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8133,14 +8205,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502112256"/>
+        <c:crossAx val="90147456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="502112256"/>
+        <c:axId val="90147456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8191,7 +8263,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502106368"/>
+        <c:crossAx val="90145920"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8360,7 +8432,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8543,6 +8615,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8552,7 +8627,7 @@
               <c:f>'model1&amp;pe'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8735,6 +8810,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>122000</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>124000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8777,7 +8855,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8960,6 +9038,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8969,7 +9050,7 @@
               <c:f>'model1&amp;pe'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -9152,6 +9233,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>193867.80757147254</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>170190.95441836005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9194,7 +9278,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9377,6 +9461,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9386,7 +9473,7 @@
               <c:f>'model1&amp;pe'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9569,6 +9656,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>71867.807571472542</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46190.954418360052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9590,11 +9680,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="502048640"/>
-        <c:axId val="502050176"/>
+        <c:axId val="90282240"/>
+        <c:axId val="90288128"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="502048640"/>
+        <c:axId val="90282240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9637,14 +9727,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502050176"/>
+        <c:crossAx val="90288128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="502050176"/>
+        <c:axId val="90288128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9695,7 +9785,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="502048640"/>
+        <c:crossAx val="90282240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10249,7 +10339,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12341,6 +12431,35 @@
         <v>71867.807571472542</v>
       </c>
     </row>
+    <row r="64" spans="1:9" ht="12.75">
+      <c r="A64" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="16">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D64" s="18">
+        <v>1806.6847444091436</v>
+      </c>
+      <c r="E64" s="18">
+        <v>153740.70049204151</v>
+      </c>
+      <c r="F64" s="18">
+        <v>170190.95441836005</v>
+      </c>
+      <c r="G64" s="18">
+        <v>124000</v>
+      </c>
+      <c r="H64" s="18">
+        <v>170190.95441836005</v>
+      </c>
+      <c r="I64" s="18">
+        <v>46190.954418360052</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12352,7 +12471,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14613,6 +14732,38 @@
         <v>66.335527216233743</v>
       </c>
     </row>
+    <row r="64" spans="1:10" ht="12.75">
+      <c r="A64" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="16">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="17">
+        <v>0</v>
+      </c>
+      <c r="D64" s="18">
+        <v>0</v>
+      </c>
+      <c r="E64" s="18">
+        <v>34651.001538842793</v>
+      </c>
+      <c r="F64" s="18">
+        <v>38358.658472178577</v>
+      </c>
+      <c r="G64" s="18">
+        <v>26000</v>
+      </c>
+      <c r="H64" s="18">
+        <v>38358.658472178577</v>
+      </c>
+      <c r="I64" s="18">
+        <v>12358.658472178577</v>
+      </c>
+      <c r="J64" s="6">
+        <v>-82.62240642203966</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14624,7 +14775,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH63"/>
+  <dimension ref="A1:AH64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -17615,6 +17766,50 @@
         <v>87.739159225273681</v>
       </c>
     </row>
+    <row r="64" spans="1:14" ht="12.75">
+      <c r="A64" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="16">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D64" s="18">
+        <v>1806.6847444091436</v>
+      </c>
+      <c r="E64" s="18">
+        <v>164841.30323118038</v>
+      </c>
+      <c r="F64" s="18">
+        <v>182479.32157648227</v>
+      </c>
+      <c r="G64" s="18">
+        <v>133000</v>
+      </c>
+      <c r="H64" s="18">
+        <v>182479.32157648227</v>
+      </c>
+      <c r="I64" s="18">
+        <v>49479.321576482267</v>
+      </c>
+      <c r="J64" s="6">
+        <v>0</v>
+      </c>
+      <c r="K64" s="6">
+        <v>3.446903866659666E-2</v>
+      </c>
+      <c r="L64" s="6">
+        <v>0.16900002956390381</v>
+      </c>
+      <c r="M64" s="6">
+        <v>6.7452480770814657E-2</v>
+      </c>
+      <c r="N64" s="1">
+        <v>51.10121714235116</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17626,7 +17821,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH63"/>
+  <dimension ref="A1:AH64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -21189,6 +21384,59 @@
         <v>96.871095864818557</v>
       </c>
     </row>
+    <row r="64" spans="1:17" ht="12.75">
+      <c r="A64" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="16">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D64" s="18">
+        <v>1806.6847444091436</v>
+      </c>
+      <c r="E64" s="18">
+        <v>156785.85798913776</v>
+      </c>
+      <c r="F64" s="18">
+        <v>173561.94374731698</v>
+      </c>
+      <c r="G64" s="18">
+        <v>126000</v>
+      </c>
+      <c r="H64" s="18">
+        <v>173561.94374731698</v>
+      </c>
+      <c r="I64" s="18">
+        <v>47561.943747316982</v>
+      </c>
+      <c r="J64" s="6">
+        <v>1.281999945640564</v>
+      </c>
+      <c r="K64" s="6">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="L64" s="6">
+        <v>1.2970000505447388</v>
+      </c>
+      <c r="M64" s="6">
+        <v>1</v>
+      </c>
+      <c r="N64" s="6">
+        <v>36.02692764800112</v>
+      </c>
+      <c r="O64" s="6">
+        <v>71.343124986463025</v>
+      </c>
+      <c r="P64" s="6">
+        <v>80.49190002957549</v>
+      </c>
+      <c r="Q64" s="1">
+        <v>53.045574900238108</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21200,7 +21448,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -23478,6 +23726,38 @@
         <v>71867.807571472542</v>
       </c>
     </row>
+    <row r="64" spans="1:10" ht="12.75">
+      <c r="A64" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="16">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="16">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E64" s="18">
+        <v>1806.6847444091436</v>
+      </c>
+      <c r="F64" s="18">
+        <v>153740.70049204151</v>
+      </c>
+      <c r="G64" s="18">
+        <v>170190.95441836005</v>
+      </c>
+      <c r="H64" s="18">
+        <v>124000</v>
+      </c>
+      <c r="I64" s="18">
+        <v>170190.95441836005</v>
+      </c>
+      <c r="J64" s="18">
+        <v>46190.954418360052</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J2"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel1.xlsx
@@ -2344,7 +2344,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2530,6 +2530,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2539,7 +2542,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2725,6 +2728,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>124000</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>126000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2767,7 +2773,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2953,6 +2959,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2962,7 +2971,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3148,6 +3157,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>170190.95441836005</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>173267.13463001052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3190,7 +3202,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3376,6 +3388,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3385,7 +3400,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3571,6 +3586,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46190.954418360052</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>47267.134630010522</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3592,11 +3610,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="548641024"/>
-        <c:axId val="566140928"/>
+        <c:axId val="413639808"/>
+        <c:axId val="417992704"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="548641024"/>
+        <c:axId val="413639808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3639,14 +3657,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566140928"/>
+        <c:crossAx val="417992704"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="566140928"/>
+        <c:axId val="417992704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3697,7 +3715,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="548641024"/>
+        <c:crossAx val="413639808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3866,7 +3884,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4052,6 +4070,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4061,7 +4082,7 @@
               <c:f>'model1&amp;CCI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4246,6 +4267,9 @@
                   <c:v>26000</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>26000</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>26000</c:v>
                 </c:pt>
               </c:numCache>
@@ -4289,7 +4313,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4475,6 +4499,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4484,7 +4511,7 @@
               <c:f>'model1&amp;CCI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4670,6 +4697,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>38358.658472178577</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>38601.214425485836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4712,7 +4742,7 @@
               <c:f>'model1&amp;CCI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4898,6 +4928,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4907,7 +4940,7 @@
               <c:f>'model1&amp;CCI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5093,6 +5126,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>12358.658472178577</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>12601.214425485836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5114,11 +5150,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="676456704"/>
-        <c:axId val="678416384"/>
+        <c:axId val="429223296"/>
+        <c:axId val="485508224"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="676456704"/>
+        <c:axId val="429223296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5161,14 +5197,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="678416384"/>
+        <c:crossAx val="485508224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="678416384"/>
+        <c:axId val="485508224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5219,7 +5255,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="676456704"/>
+        <c:crossAx val="429223296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5388,7 +5424,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5574,6 +5610,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5583,7 +5622,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5769,6 +5808,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>133000</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>135000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5811,7 +5853,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5997,6 +6039,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6006,7 +6051,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6192,6 +6237,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>182479.32157648227</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>185633.20566854317</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6234,7 +6282,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6420,6 +6468,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6429,7 +6480,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6615,6 +6666,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>49479.321576482267</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>50633.205668543174</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6636,11 +6690,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="80539648"/>
-        <c:axId val="80541184"/>
+        <c:axId val="526389248"/>
+        <c:axId val="526390784"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="80539648"/>
+        <c:axId val="526389248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6683,14 +6737,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80541184"/>
+        <c:crossAx val="526390784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="80541184"/>
+        <c:axId val="526390784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6741,7 +6795,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80539648"/>
+        <c:crossAx val="526389248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6910,7 +6964,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7096,6 +7150,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7105,7 +7162,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7291,6 +7348,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>126000</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>128000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7333,7 +7393,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7519,6 +7579,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7528,7 +7591,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7714,6 +7777,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>173561.94374731698</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>176659.43996851629</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7756,7 +7822,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7942,6 +8008,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7951,7 +8020,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8137,6 +8206,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>47561.943747316982</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>48659.439968516293</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8158,11 +8230,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="90145920"/>
-        <c:axId val="90147456"/>
+        <c:axId val="526414976"/>
+        <c:axId val="526416512"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="90145920"/>
+        <c:axId val="526414976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8205,14 +8277,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90147456"/>
+        <c:crossAx val="526416512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="90147456"/>
+        <c:axId val="526416512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8263,7 +8335,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90145920"/>
+        <c:crossAx val="526414976"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8432,7 +8504,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8618,6 +8690,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8627,7 +8702,7 @@
               <c:f>'model1&amp;pe'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8813,6 +8888,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>124000</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>126000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8855,7 +8933,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9041,6 +9119,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9050,7 +9131,7 @@
               <c:f>'model1&amp;pe'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -9236,6 +9317,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>170190.95441836005</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>173267.13463001052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9278,7 +9362,7 @@
               <c:f>'model1&amp;pe'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9464,6 +9548,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9473,7 +9560,7 @@
               <c:f>'model1&amp;pe'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9659,6 +9746,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46190.954418360052</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>47267.134630010522</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9680,11 +9770,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="90282240"/>
-        <c:axId val="90288128"/>
+        <c:axId val="526641792"/>
+        <c:axId val="526647680"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="90282240"/>
+        <c:axId val="526641792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9727,14 +9817,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90288128"/>
+        <c:crossAx val="526647680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="90288128"/>
+        <c:axId val="526647680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9785,7 +9875,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90282240"/>
+        <c:crossAx val="526641792"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10339,7 +10429,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12460,6 +12550,35 @@
         <v>46190.954418360052</v>
       </c>
     </row>
+    <row r="65" spans="1:9" ht="12.75">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="16">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D65" s="18">
+        <v>1795.3321963862891</v>
+      </c>
+      <c r="E65" s="18">
+        <v>155536.0326884278</v>
+      </c>
+      <c r="F65" s="18">
+        <v>173267.13463001052</v>
+      </c>
+      <c r="G65" s="18">
+        <v>126000</v>
+      </c>
+      <c r="H65" s="18">
+        <v>173267.13463001052</v>
+      </c>
+      <c r="I65" s="18">
+        <v>47267.134630010522</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12471,7 +12590,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14764,6 +14883,38 @@
         <v>-82.62240642203966</v>
       </c>
     </row>
+    <row r="65" spans="1:10" ht="12.75">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="16">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="17">
+        <v>0</v>
+      </c>
+      <c r="D65" s="18">
+        <v>0</v>
+      </c>
+      <c r="E65" s="18">
+        <v>34651.001538842793</v>
+      </c>
+      <c r="F65" s="18">
+        <v>38601.214425485836</v>
+      </c>
+      <c r="G65" s="18">
+        <v>26000</v>
+      </c>
+      <c r="H65" s="18">
+        <v>38601.214425485836</v>
+      </c>
+      <c r="I65" s="18">
+        <v>12601.214425485836</v>
+      </c>
+      <c r="J65" s="6">
+        <v>-90.561561933820059</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14775,7 +14926,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH64"/>
+  <dimension ref="A1:AH65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -17810,6 +17961,50 @@
         <v>51.10121714235116</v>
       </c>
     </row>
+    <row r="65" spans="1:14" ht="12.75">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="16">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D65" s="18">
+        <v>1795.3321963862891</v>
+      </c>
+      <c r="E65" s="18">
+        <v>166636.63542756668</v>
+      </c>
+      <c r="F65" s="18">
+        <v>185633.20566854317</v>
+      </c>
+      <c r="G65" s="18">
+        <v>135000</v>
+      </c>
+      <c r="H65" s="18">
+        <v>185633.20566854317</v>
+      </c>
+      <c r="I65" s="18">
+        <v>50633.205668543174</v>
+      </c>
+      <c r="J65" s="6">
+        <v>6.999969482421875E-3</v>
+      </c>
+      <c r="K65" s="6">
+        <v>2.9890860469234198E-2</v>
+      </c>
+      <c r="L65" s="6">
+        <v>6.999969482421875E-3</v>
+      </c>
+      <c r="M65" s="6">
+        <v>5.7377062222749194E-2</v>
+      </c>
+      <c r="N65" s="1">
+        <v>52.095487833085492</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17821,7 +18016,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH64"/>
+  <dimension ref="A1:AH65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -21437,6 +21632,59 @@
         <v>53.045574900238108</v>
       </c>
     </row>
+    <row r="65" spans="1:17" ht="12.75">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="16">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="17">
+        <v>2000</v>
+      </c>
+      <c r="D65" s="18">
+        <v>1795.3321963862891</v>
+      </c>
+      <c r="E65" s="18">
+        <v>158581.19018552406</v>
+      </c>
+      <c r="F65" s="18">
+        <v>176659.43996851629</v>
+      </c>
+      <c r="G65" s="18">
+        <v>128000</v>
+      </c>
+      <c r="H65" s="18">
+        <v>176659.43996851629</v>
+      </c>
+      <c r="I65" s="18">
+        <v>48659.439968516293</v>
+      </c>
+      <c r="J65" s="6">
+        <v>1.1759999990463257</v>
+      </c>
+      <c r="K65" s="6">
+        <v>1.093000054359436</v>
+      </c>
+      <c r="L65" s="6">
+        <v>1.2970000505447388</v>
+      </c>
+      <c r="M65" s="6">
+        <v>1.031000018119812</v>
+      </c>
+      <c r="N65" s="6">
+        <v>31.202982920806502</v>
+      </c>
+      <c r="O65" s="6">
+        <v>57.963077631244182</v>
+      </c>
+      <c r="P65" s="6">
+        <v>72.982292563465052</v>
+      </c>
+      <c r="Q65" s="1">
+        <v>27.924647766802451</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21448,7 +21696,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -23758,6 +24006,38 @@
         <v>46190.954418360052</v>
       </c>
     </row>
+    <row r="65" spans="1:10" ht="12.75">
+      <c r="A65" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="16">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="16">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="17">
+        <v>2000</v>
+      </c>
+      <c r="E65" s="18">
+        <v>1795.3321963862891</v>
+      </c>
+      <c r="F65" s="18">
+        <v>155536.0326884278</v>
+      </c>
+      <c r="G65" s="18">
+        <v>173267.13463001052</v>
+      </c>
+      <c r="H65" s="18">
+        <v>126000</v>
+      </c>
+      <c r="I65" s="18">
+        <v>173267.13463001052</v>
+      </c>
+      <c r="J65" s="18">
+        <v>47267.134630010522</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J2"/>
   <phoneticPr fontId="1" type="noConversion"/>
